--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47DE690B-8DE4-451B-A65E-D892FD83AE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3202FCF-1469-4AFB-9374-9C3EB9B84D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="790" windowWidth="16920" windowHeight="14250" xr2:uid="{DE01A25D-5758-4EDD-A60D-1EC9E64E5B14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{14E0BC16-A90A-41A2-B4F2-7C9B1538916F}"/>
   </bookViews>
   <sheets>
-    <sheet name="情報アクセシビリティ自己評価様式" sheetId="1" r:id="rId1"/>
-    <sheet name="様式作成時の技術基準" sheetId="2" r:id="rId2"/>
+    <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
+    <sheet name="様式作成時の技術基準" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">様式作成時の技術基準!$A$1:$M$90</definedName>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -55,7 +58,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -65,7 +68,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -74,7 +77,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -84,7 +87,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -93,7 +96,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -103,7 +106,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -112,7 +115,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -139,7 +142,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -151,7 +154,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -174,7 +177,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -185,12 +188,13 @@
   </si>
   <si>
     <t>Dynamics 365 Warehouse Management(Android,Windows(UWP),IOS)</t>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -206,7 +210,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -221,7 +225,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
@@ -237,7 +241,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -254,7 +258,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -265,7 +269,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -281,7 +285,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -346,7 +350,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -358,7 +362,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -422,7 +426,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -438,7 +442,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -448,7 +452,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -457,7 +461,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -548,7 +552,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -564,7 +568,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -655,7 +659,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -668,7 +672,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -722,7 +726,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -779,7 +783,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -791,7 +795,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -801,7 +805,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -810,7 +814,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -824,7 +828,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -1589,7 +1593,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1630,19 +1634,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1665,38 +1676,6 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1704,17 +1683,35 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.5"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2044,188 +2041,191 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2249,16 +2249,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2291,15 +2291,15 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>43760</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>34688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EED64EE-CD31-4A91-842C-4066AA9CC0E3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A871F353-EC75-4F33-9083-4D8FB3861FA7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2321,8 +2321,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6115050" y="1156389"/>
-          <a:ext cx="3505200" cy="1541671"/>
+          <a:off x="6115050" y="1105589"/>
+          <a:ext cx="3505200" cy="1538949"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2650,228 +2650,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F42DE8EA-1CF5-4814-875E-C0ABD4D5250F}">
-  <sheetPr codeName="Sheet781">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEDD939D-7F71-4D8D-BFB5-992408D2C94C}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="2"/>
-    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="2"/>
+    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="3"/>
+    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -2989,13 +2989,13 @@
       <c r="D24" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
@@ -3004,11 +3004,11 @@
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
@@ -3019,13 +3019,13 @@
       <c r="D26" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
@@ -3034,11 +3034,11 @@
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
@@ -3215,28 +3215,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3286,15 +3286,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3313,11 +3313,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="4"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3335,7 +3335,8 @@
       <c r="H48" s="42"/>
       <c r="I48" s="42"/>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="58"/>
       <c r="B49" s="42"/>
       <c r="C49" s="42"/>
       <c r="D49" s="42"/>
@@ -3345,7 +3346,8 @@
       <c r="H49" s="42"/>
       <c r="I49" s="42"/>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="58"/>
       <c r="B50" s="42"/>
       <c r="C50" s="42"/>
       <c r="D50" s="42"/>
@@ -3355,7 +3357,8 @@
       <c r="H50" s="42"/>
       <c r="I50" s="42"/>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="58"/>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="42"/>
@@ -3365,7 +3368,8 @@
       <c r="H51" s="42"/>
       <c r="I51" s="42"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="58"/>
       <c r="B52" s="42"/>
       <c r="C52" s="42"/>
       <c r="D52" s="42"/>
@@ -3375,7 +3379,8 @@
       <c r="H52" s="42"/>
       <c r="I52" s="42"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="58"/>
       <c r="B53" s="42"/>
       <c r="C53" s="42"/>
       <c r="D53" s="42"/>
@@ -3385,7 +3390,8 @@
       <c r="H53" s="42"/>
       <c r="I53" s="42"/>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="58"/>
       <c r="B54" s="42"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
@@ -3458,7 +3464,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{EB255DAF-E663-4945-85C1-539B86602692}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{DCEE792F-D179-4081-8E6D-BC52ADAB8EF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3467,2252 +3473,2252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298BA326-C99E-4A07-A17E-81CEA6A3C32A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDED0A5F-E0D4-46F1-A835-0BE0A3061AA0}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.08203125" style="63" customWidth="1"/>
-    <col min="3" max="3" width="33.08203125" style="63" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.08203125" style="64" customWidth="1"/>
+    <col min="3" max="3" width="33.08203125" style="64" customWidth="1"/>
     <col min="4" max="13" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="60" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="61">
+      <c r="A2" s="62">
         <v>301</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="65" t="s">
+      <c r="D2" s="65"/>
+      <c r="E2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="65" t="s">
+      <c r="G2" s="67"/>
+      <c r="H2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="65" t="s">
+      <c r="J2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="65" t="s">
+      <c r="L2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="65" t="s">
+      <c r="M2" s="66" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="61">
+      <c r="A3" s="62">
         <v>302</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="64">
+      <c r="A4" s="65">
         <v>302.10000000000002</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="65"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="64">
+      <c r="A5" s="65">
         <v>302.2</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="67"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="68"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="64">
+      <c r="A6" s="65">
         <v>302.3</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="68"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="64">
+      <c r="A7" s="65">
         <v>302.39999999999998</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="64">
+      <c r="A8" s="65">
         <v>302.5</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="64">
+      <c r="A9" s="65">
         <v>302.60000000000002</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="64">
+      <c r="A10" s="65">
         <v>302.7</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="65"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="64">
+      <c r="A11" s="65">
         <v>302.8</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64" t="s">
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="64"/>
+      <c r="L11" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="64">
+      <c r="A12" s="65">
         <v>302.89999999999998</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="64">
+      <c r="A13" s="65">
         <v>402</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-    </row>
-    <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="68">
+      <c r="D13" s="65"/>
+      <c r="E13" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="67"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+    </row>
+    <row r="14" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="69">
         <v>402.1</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="64">
+      <c r="A15" s="65">
         <v>402.2</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="65"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="65"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="68"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="68"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="65"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="64">
+      <c r="A21" s="65">
         <v>402.3</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="65"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="65"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
     </row>
     <row r="24" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="64">
+      <c r="A24" s="65">
         <v>402.4</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="68"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="64">
+      <c r="A25" s="65">
         <v>402.5</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="67"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="68"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="64">
+      <c r="A26" s="65">
         <v>403</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="66"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="64">
+      <c r="A27" s="65">
         <v>403.1</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="64">
+      <c r="A28" s="65">
         <v>404</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="66"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="66"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="64">
+      <c r="A29" s="65">
         <v>404.1</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="64">
+      <c r="A30" s="65">
         <v>405</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="64">
+      <c r="A31" s="65">
         <v>405.1</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="64">
+      <c r="A32" s="65">
         <v>406</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="64"/>
-      <c r="E32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M32" s="65" t="s">
+      <c r="D32" s="65"/>
+      <c r="E32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="66"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="66" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="64">
+      <c r="A33" s="65">
         <v>406.1</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="64"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="64">
+      <c r="A34" s="65">
         <v>407</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="67"/>
+      <c r="H34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="66"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="64">
+      <c r="A35" s="65">
         <v>407.1</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="66"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="64">
+      <c r="A36" s="65">
         <v>407.2</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="68"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
     </row>
     <row r="37" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="64">
+      <c r="A37" s="65">
         <v>407.3</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="64"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="65"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="64">
+      <c r="A38" s="65">
         <v>407.4</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L38" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L38" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="65"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="64">
+      <c r="A39" s="65">
         <v>407.5</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" s="67"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M39" s="64"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="68"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="65"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="64">
+      <c r="A40" s="65">
         <v>407.6</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L40" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M40" s="64"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="65"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="64">
+      <c r="A41" s="65">
         <v>407.7</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="64"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="65"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="64">
+      <c r="A42" s="65">
         <v>407.8</v>
       </c>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L42" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M42" s="64"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L42" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="65"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="64">
+      <c r="A43" s="65">
         <v>408</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L43" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M43" s="65"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L43" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="66"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="64">
+      <c r="A44" s="65">
         <v>408.1</v>
       </c>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="66"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="64">
+      <c r="A45" s="65">
         <v>408.2</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="66"/>
+      <c r="K45" s="66"/>
+      <c r="L45" s="66"/>
+      <c r="M45" s="66"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="64">
+      <c r="A46" s="65">
         <v>408.3</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64"/>
-      <c r="J46" s="64"/>
-      <c r="K46" s="64"/>
-      <c r="L46" s="64"/>
-      <c r="M46" s="64"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="64">
+      <c r="A47" s="65">
         <v>409</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="C47" s="63" t="s">
+      <c r="C47" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" s="65"/>
-      <c r="G47" s="66"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
+      <c r="M47" s="66"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="64">
+      <c r="A48" s="65">
         <v>409.1</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C48" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D48" s="64"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65"/>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="66"/>
+      <c r="M48" s="66"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="64">
+      <c r="A49" s="65">
         <v>410</v>
       </c>
-      <c r="B49" s="63" t="s">
+      <c r="B49" s="64" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="D49" s="64"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G49" s="66"/>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" s="67"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="66"/>
+      <c r="M49" s="66"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="64">
+      <c r="A50" s="65">
         <v>410.1</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="63" t="s">
+      <c r="C50" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="64"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="66"/>
+      <c r="M50" s="66"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="64">
+      <c r="A51" s="65">
         <v>411</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="64"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="66"/>
-      <c r="H51" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I51" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I51" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J51" s="66"/>
+      <c r="K51" s="66"/>
+      <c r="L51" s="66"/>
+      <c r="M51" s="66"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="64">
+      <c r="A52" s="65">
         <v>411.1</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="66"/>
+      <c r="J52" s="66"/>
+      <c r="K52" s="66"/>
+      <c r="L52" s="66"/>
+      <c r="M52" s="66"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="64">
+      <c r="A53" s="65">
         <v>412</v>
       </c>
-      <c r="B53" s="63" t="s">
+      <c r="B53" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F53" s="65"/>
-      <c r="G53" s="66"/>
-      <c r="H53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M53" s="65"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" s="66"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J53" s="66"/>
+      <c r="K53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M53" s="66"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="64">
+      <c r="A54" s="65">
         <v>412.1</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="66"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="66"/>
+      <c r="L54" s="66"/>
+      <c r="M54" s="66"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="64">
+      <c r="A55" s="65">
         <v>412.2</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J55" s="64"/>
-      <c r="K55" s="64"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="64"/>
+      <c r="D55" s="65"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J55" s="65"/>
+      <c r="K55" s="65"/>
+      <c r="L55" s="65"/>
+      <c r="M55" s="65"/>
     </row>
     <row r="56" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="64">
+      <c r="A56" s="65">
         <v>412.3</v>
       </c>
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J56" s="64"/>
-      <c r="K56" s="64"/>
-      <c r="L56" s="64"/>
-      <c r="M56" s="64"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="65"/>
+      <c r="K56" s="65"/>
+      <c r="L56" s="65"/>
+      <c r="M56" s="65"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="64">
+      <c r="A57" s="65">
         <v>412.4</v>
       </c>
-      <c r="B57" s="63" t="s">
+      <c r="B57" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J57" s="64"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
+      <c r="D57" s="65"/>
+      <c r="E57" s="65"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="68"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="65"/>
+      <c r="M57" s="65"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="64">
+      <c r="A58" s="65">
         <v>412.5</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="67"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="68"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="64">
+      <c r="A59" s="65">
         <v>412.6</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59" s="67"/>
-      <c r="H59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J59" s="64"/>
-      <c r="K59" s="64"/>
-      <c r="L59" s="64"/>
-      <c r="M59" s="64"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" s="68"/>
+      <c r="H59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="64">
+      <c r="A60" s="65">
         <v>412.7</v>
       </c>
-      <c r="B60" s="63" t="s">
+      <c r="B60" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="63" t="s">
+      <c r="C60" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I60" s="64"/>
-      <c r="J60" s="64"/>
-      <c r="K60" s="64"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="64"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="68"/>
+      <c r="H60" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="65"/>
+      <c r="L60" s="65"/>
+      <c r="M60" s="65"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="64">
+      <c r="A61" s="65">
         <v>413</v>
       </c>
-      <c r="B61" s="63" t="s">
+      <c r="B61" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="64" t="s">
         <v>174</v>
       </c>
-      <c r="D61" s="64"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I61" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J61" s="65"/>
-      <c r="K61" s="65"/>
-      <c r="L61" s="65"/>
-      <c r="M61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I61" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
+      <c r="M61" s="66"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="64">
+      <c r="A62" s="65">
         <v>411.1</v>
       </c>
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="C62" s="63" t="s">
+      <c r="C62" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="65"/>
-      <c r="I62" s="65"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="65"/>
-      <c r="L62" s="65"/>
-      <c r="M62" s="65"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="67"/>
+      <c r="H62" s="66"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="66"/>
+      <c r="K62" s="66"/>
+      <c r="L62" s="66"/>
+      <c r="M62" s="66"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="64">
+      <c r="A63" s="65">
         <v>414</v>
       </c>
-      <c r="B63" s="63" t="s">
+      <c r="B63" s="64" t="s">
         <v>177</v>
       </c>
-      <c r="C63" s="63" t="s">
+      <c r="C63" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F63" s="65"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="65"/>
-      <c r="I63" s="65"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="65"/>
-      <c r="M63" s="65"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="66"/>
+      <c r="G63" s="67"/>
+      <c r="H63" s="66"/>
+      <c r="I63" s="66"/>
+      <c r="J63" s="66"/>
+      <c r="K63" s="66"/>
+      <c r="L63" s="66"/>
+      <c r="M63" s="66"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="64">
+      <c r="A64" s="65">
         <v>412.1</v>
       </c>
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="C64" s="63" t="s">
+      <c r="C64" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="65"/>
-      <c r="I64" s="65"/>
-      <c r="J64" s="65"/>
-      <c r="K64" s="65"/>
-      <c r="L64" s="65"/>
-      <c r="M64" s="65"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="66"/>
+      <c r="I64" s="66"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="66"/>
+      <c r="M64" s="66"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="64">
+      <c r="A65" s="65">
         <v>415</v>
       </c>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="64"/>
-      <c r="E65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F65" s="65"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J65" s="65"/>
-      <c r="K65" s="65"/>
-      <c r="L65" s="65"/>
-      <c r="M65" s="65"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="66"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J65" s="66"/>
+      <c r="K65" s="66"/>
+      <c r="L65" s="66"/>
+      <c r="M65" s="66"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="64">
+      <c r="A66" s="65">
         <v>413.1</v>
       </c>
-      <c r="B66" s="63" t="s">
+      <c r="B66" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="63" t="s">
+      <c r="C66" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="65"/>
-      <c r="I66" s="65"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="65"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="66"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="66"/>
+      <c r="K66" s="66"/>
+      <c r="L66" s="66"/>
+      <c r="M66" s="66"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="64">
+      <c r="A67" s="65">
         <v>502</v>
       </c>
-      <c r="B67" s="63" t="s">
+      <c r="B67" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="D67" s="64"/>
-      <c r="E67" s="65" t="s">
+      <c r="D67" s="65"/>
+      <c r="E67" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="65" t="s">
+      <c r="F67" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="G67" s="66"/>
-      <c r="H67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J67" s="65"/>
-      <c r="K67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M67" s="65"/>
+      <c r="G67" s="67"/>
+      <c r="H67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" s="66"/>
+      <c r="K67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" s="66"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="64">
+      <c r="A68" s="65">
         <v>502.1</v>
       </c>
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C68" s="63" t="s">
+      <c r="C68" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="64"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="65"/>
-      <c r="L68" s="65"/>
-      <c r="M68" s="65"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="66"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="66"/>
+      <c r="K68" s="66"/>
+      <c r="L68" s="66"/>
+      <c r="M68" s="66"/>
     </row>
     <row r="69" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="64">
+      <c r="A69" s="65">
         <v>502.2</v>
       </c>
-      <c r="B69" s="63" t="s">
+      <c r="B69" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C69" s="63" t="s">
+      <c r="C69" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F69" s="64"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J69" s="64"/>
-      <c r="K69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M69" s="64"/>
+      <c r="D69" s="65"/>
+      <c r="E69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" s="65"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J69" s="65"/>
+      <c r="K69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="65"/>
     </row>
     <row r="70" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="64">
+      <c r="A70" s="65">
         <v>502.3</v>
       </c>
-      <c r="B70" s="63" t="s">
+      <c r="B70" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C70" s="63" t="s">
+      <c r="C70" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F70" s="64"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="64"/>
-      <c r="J70" s="64"/>
-      <c r="K70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M70" s="64"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F70" s="65"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="65"/>
+      <c r="I70" s="65"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M70" s="65"/>
     </row>
     <row r="71" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="64">
+      <c r="A71" s="65">
         <v>502.4</v>
       </c>
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="C71" s="63" t="s">
+      <c r="C71" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G71" s="67"/>
-      <c r="H71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J71" s="64"/>
-      <c r="K71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M71" s="64"/>
+      <c r="D71" s="65"/>
+      <c r="E71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G71" s="68"/>
+      <c r="H71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J71" s="65"/>
+      <c r="K71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="64" t="s">
+      <c r="A72" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="63" t="s">
+      <c r="B72" s="64" t="s">
         <v>192</v>
       </c>
-      <c r="C72" s="63" t="s">
+      <c r="C72" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64"/>
-      <c r="J72" s="64"/>
-      <c r="K72" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L72" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M72" s="64"/>
+      <c r="D72" s="65"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="65"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="65"/>
+      <c r="K72" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L72" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="64" t="s">
+      <c r="A73" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="B73" s="63" t="s">
+      <c r="B73" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C73" s="63" t="s">
+      <c r="C73" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="64"/>
-      <c r="J73" s="64"/>
-      <c r="K73" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L73" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M73" s="64"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L73" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="64" t="s">
+      <c r="A74" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="B74" s="63" t="s">
+      <c r="B74" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="C74" s="63" t="s">
+      <c r="C74" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="D74" s="64"/>
-      <c r="E74" s="64"/>
-      <c r="F74" s="64"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="64"/>
-      <c r="I74" s="64"/>
-      <c r="J74" s="64"/>
-      <c r="K74" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L74" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M74" s="64"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="65"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L74" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="64" t="s">
+      <c r="A75" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C75" s="63" t="s">
+      <c r="C75" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I75" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="64"/>
-      <c r="M75" s="64"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="65"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="68"/>
+      <c r="H75" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I75" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J75" s="65"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
+      <c r="M75" s="65"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="64" t="s">
+      <c r="A76" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="B76" s="63" t="s">
+      <c r="B76" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="C76" s="63" t="s">
+      <c r="C76" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G76" s="67"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
-      <c r="L76" s="64"/>
-      <c r="M76" s="64"/>
+      <c r="D76" s="65"/>
+      <c r="E76" s="65"/>
+      <c r="F76" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G76" s="68"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J76" s="65"/>
+      <c r="K76" s="65"/>
+      <c r="L76" s="65"/>
+      <c r="M76" s="65"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="64" t="s">
+      <c r="A77" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="63" t="s">
+      <c r="C77" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G77" s="67"/>
-      <c r="H77" s="64"/>
-      <c r="I77" s="64"/>
-      <c r="J77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="K77" s="64"/>
-      <c r="L77" s="64"/>
-      <c r="M77" s="64"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G77" s="68"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="65"/>
+      <c r="J77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="K77" s="65"/>
+      <c r="L77" s="65"/>
+      <c r="M77" s="65"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="64" t="s">
+      <c r="A78" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="B78" s="63" t="s">
+      <c r="B78" s="64" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="63" t="s">
+      <c r="C78" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I78" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J78" s="64"/>
-      <c r="K78" s="64"/>
-      <c r="L78" s="64"/>
-      <c r="M78" s="64"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="68"/>
+      <c r="H78" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I78" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J78" s="65"/>
+      <c r="K78" s="65"/>
+      <c r="L78" s="65"/>
+      <c r="M78" s="65"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="64">
+      <c r="A79" s="65">
         <v>503</v>
       </c>
-      <c r="B79" s="63" t="s">
+      <c r="B79" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="C79" s="63" t="s">
+      <c r="C79" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G79" s="66"/>
-      <c r="H79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J79" s="65"/>
-      <c r="K79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M79" s="65"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" s="67"/>
+      <c r="H79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J79" s="66"/>
+      <c r="K79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M79" s="66"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="64">
+      <c r="A80" s="65">
         <v>503.1</v>
       </c>
-      <c r="B80" s="63" t="s">
+      <c r="B80" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="63" t="s">
+      <c r="C80" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-      <c r="J80" s="65"/>
-      <c r="K80" s="65"/>
-      <c r="L80" s="65"/>
-      <c r="M80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="66"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="66"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="66"/>
+      <c r="K80" s="66"/>
+      <c r="L80" s="66"/>
+      <c r="M80" s="66"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="64">
+      <c r="A81" s="65">
         <v>503.2</v>
       </c>
-      <c r="B81" s="63" t="s">
+      <c r="B81" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="63" t="s">
+      <c r="C81" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G81" s="67"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="64"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
-      <c r="M81" s="64"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" s="68"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="64">
+      <c r="A82" s="65">
         <v>503.3</v>
       </c>
-      <c r="B82" s="63" t="s">
+      <c r="B82" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="C82" s="63" t="s">
+      <c r="C82" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F82" s="64"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="64"/>
-      <c r="J82" s="64"/>
-      <c r="K82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M82" s="64"/>
+      <c r="D82" s="65"/>
+      <c r="E82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F82" s="65"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M82" s="65"/>
     </row>
     <row r="83" spans="1:13" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="64">
+      <c r="A83" s="65">
         <v>503.4</v>
       </c>
-      <c r="B83" s="63" t="s">
+      <c r="B83" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="C83" s="63" t="s">
+      <c r="C83" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="67"/>
-      <c r="H83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J83" s="64"/>
-      <c r="K83" s="64"/>
-      <c r="L83" s="64"/>
-      <c r="M83" s="64"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F83" s="65"/>
+      <c r="G83" s="68"/>
+      <c r="H83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J83" s="65"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="64">
+      <c r="A84" s="65">
         <v>504</v>
       </c>
-      <c r="B84" s="63" t="s">
+      <c r="B84" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="C84" s="63" t="s">
+      <c r="C84" s="64" t="s">
         <v>221</v>
       </c>
-      <c r="D84" s="64"/>
-      <c r="E84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G84" s="66"/>
-      <c r="H84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J84" s="65"/>
-      <c r="K84" s="65"/>
-      <c r="L84" s="65"/>
-      <c r="M84" s="65"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G84" s="67"/>
+      <c r="H84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J84" s="66"/>
+      <c r="K84" s="66"/>
+      <c r="L84" s="66"/>
+      <c r="M84" s="66"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="64">
+      <c r="A85" s="65">
         <v>504.1</v>
       </c>
-      <c r="B85" s="63" t="s">
+      <c r="B85" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="63" t="s">
+      <c r="C85" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D85" s="64"/>
-      <c r="E85" s="65"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="65"/>
-      <c r="I85" s="65"/>
-      <c r="J85" s="65"/>
-      <c r="K85" s="65"/>
-      <c r="L85" s="65"/>
-      <c r="M85" s="65"/>
+      <c r="D85" s="65"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="67"/>
+      <c r="H85" s="66"/>
+      <c r="I85" s="66"/>
+      <c r="J85" s="66"/>
+      <c r="K85" s="66"/>
+      <c r="L85" s="66"/>
+      <c r="M85" s="66"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="64">
+      <c r="A86" s="65">
         <v>504.2</v>
       </c>
-      <c r="B86" s="63" t="s">
+      <c r="B86" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="C86" s="63" t="s">
+      <c r="C86" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="D86" s="64"/>
-      <c r="E86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G86" s="67"/>
-      <c r="H86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J86" s="64"/>
-      <c r="K86" s="64"/>
-      <c r="L86" s="64"/>
-      <c r="M86" s="64"/>
+      <c r="D86" s="65"/>
+      <c r="E86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G86" s="68"/>
+      <c r="H86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J86" s="65"/>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="64" t="s">
+      <c r="A87" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="C87" s="63" t="s">
+      <c r="C87" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F87" s="64"/>
-      <c r="G87" s="67"/>
-      <c r="H87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J87" s="64"/>
-      <c r="K87" s="64"/>
-      <c r="L87" s="64"/>
-      <c r="M87" s="64"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F87" s="65"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J87" s="65"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="64" t="s">
+      <c r="A88" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="B88" s="63" t="s">
+      <c r="B88" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C88" s="63" t="s">
+      <c r="C88" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F88" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G88" s="67"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="64"/>
-      <c r="J88" s="64"/>
-      <c r="K88" s="64"/>
-      <c r="L88" s="64"/>
-      <c r="M88" s="64"/>
+      <c r="D88" s="65"/>
+      <c r="E88" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F88" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G88" s="68"/>
+      <c r="H88" s="65"/>
+      <c r="I88" s="65"/>
+      <c r="J88" s="65"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="64">
+      <c r="A89" s="65">
         <v>504.3</v>
       </c>
-      <c r="B89" s="63" t="s">
+      <c r="B89" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="C89" s="63" t="s">
+      <c r="C89" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G89" s="67"/>
-      <c r="H89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="64"/>
-      <c r="M89" s="64"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G89" s="68"/>
+      <c r="H89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J89" s="65"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="64">
+      <c r="A90" s="65">
         <v>504.4</v>
       </c>
-      <c r="B90" s="63" t="s">
+      <c r="B90" s="64" t="s">
         <v>232</v>
       </c>
-      <c r="C90" s="63" t="s">
+      <c r="C90" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G90" s="67"/>
-      <c r="H90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J90" s="64"/>
-      <c r="K90" s="64"/>
-      <c r="L90" s="64"/>
-      <c r="M90" s="64"/>
+      <c r="D90" s="65"/>
+      <c r="E90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G90" s="68"/>
+      <c r="H90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J90" s="65"/>
+      <c r="K90" s="65"/>
+      <c r="L90" s="65"/>
+      <c r="M90" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M90" xr:uid="{C6D2D344-3C1F-449C-B697-53FB90F953F5}"/>

--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3202FCF-1469-4AFB-9374-9C3EB9B84D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C674D957-D56F-4628-AC75-8E96521263D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{14E0BC16-A90A-41A2-B4F2-7C9B1538916F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{16BEE822-CF34-4039-B6E4-8788894F1B74}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2025</t>
+      <t>2026</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>12</t>
+      <t>6</t>
     </r>
     <r>
       <rPr>
@@ -230,12 +230,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>は、使いやすく直感的なデザインと強化された機能をもつ倉庫管理ソリューションです。</t>
-    </r>
-    <rPh sb="85" eb="89">
-      <t>ソウコカンリ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
+      <t>は、倉庫作業向けモバイルアプリで、直感的で使いやすい新デザインを採用し、倉庫管理ロジックの強化で処理を効率化します。ユーザビリティ調査に基づき、作業を正確に、より効率的に完了できます。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2291,15 +2287,15 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>34688</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>914617</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A871F353-EC75-4F33-9083-4D8FB3861FA7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9573F740-9D20-410F-A1B8-5CC13FDD5075}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2322,7 +2318,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6115050" y="1105589"/>
-          <a:ext cx="3505200" cy="1538949"/>
+          <a:ext cx="3505200" cy="1542578"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2650,7 +2646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEDD939D-7F71-4D8D-BFB5-992408D2C94C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CC09B8-FDFD-4661-847F-7C57CF800F9F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2782,7 +2778,7 @@
       <c r="H9" s="18"/>
       <c r="I9" s="19"/>
     </row>
-    <row r="10" spans="1:9" ht="69" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
@@ -3464,7 +3460,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{DCEE792F-D179-4081-8E6D-BC52ADAB8EF9}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{E6142080-3935-4B44-BAA3-8D59479D13E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3473,7 +3469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDED0A5F-E0D4-46F1-A835-0BE0A3061AA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F9B2DA-0CB1-4CCA-AD8A-5B2B8B10CC50}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C674D957-D56F-4628-AC75-8E96521263D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB5DBFA4-B4FF-489B-9CBC-696C8047B89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{16BEE822-CF34-4039-B6E4-8788894F1B74}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{71780A4C-AAF4-4321-912C-AC32F9677B42}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -37,6 +37,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
   <si>
@@ -73,7 +95,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026</t>
+      <t>2025</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +133,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>6</t>
+      <t>12</t>
     </r>
     <r>
       <rPr>
@@ -188,7 +210,6 @@
   </si>
   <si>
     <t>Dynamics 365 Warehouse Management(Android,Windows(UWP),IOS)</t>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -275,7 +296,6 @@
   </si>
   <si>
     <t>https://learn.microsoft.com/ja-jp/dynamics365/supply-chain/warehousing/warehouse-management-overview</t>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -1680,7 +1700,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2275,59 +2295,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>184839</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>914617</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9573F740-9D20-410F-A1B8-5CC13FDD5075}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6115050" y="1105589"/>
-          <a:ext cx="3505200" cy="1542578"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2646,8 +2675,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CC09B8-FDFD-4661-847F-7C57CF800F9F}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EB6FF7-0DB4-4FE2-8363-9025B0F17256}">
+  <sheetPr codeName="Sheet235">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2713,7 +2742,9 @@
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="H4" s="12"/>
       <c r="I4" s="13"/>
     </row>
@@ -2778,7 +2809,7 @@
       <c r="H9" s="18"/>
       <c r="I9" s="19"/>
     </row>
-    <row r="10" spans="1:9" ht="73.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
@@ -3460,16 +3491,15 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{E6142080-3935-4B44-BAA3-8D59479D13E3}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{564F184E-B751-4995-894F-BED036118835}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3F9B2DA-0CB1-4CCA-AD8A-5B2B8B10CC50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE49694-1814-41DE-B121-884D6BE90C2E}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB5DBFA4-B4FF-489B-9CBC-696C8047B89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{668931E9-7E53-4CCA-92D0-AC3CCEA5728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{71780A4C-AAF4-4321-912C-AC32F9677B42}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{7C940804-A9F8-4AB4-9BC6-A2510CCAAA97}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -60,798 +60,196 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービスのアクセシビリティ自己評価様式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>作成日：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品画像</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>企業・団体名</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日本マイクロソフト株式会社</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+  <si>
+    <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
+  </si>
+  <si>
+    <t>作成日：2026年8月6日</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品画像</t>
+  </si>
+  <si>
+    <t>企業・団体名</t>
+  </si>
+  <si>
+    <t>日本マイクロソフト株式会社</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス名称</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ICT機器・サービス名称</t>
   </si>
   <si>
     <t>Dynamics 365 Warehouse Management(Android,Windows(UWP),IOS)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>型番</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dynamics 365 Warehouse Management(Android,Windows(UWP),IOS)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は、倉庫作業向けモバイルアプリで、直感的で使いやすい新デザインを採用し、倉庫管理ロジックの強化で処理を効率化します。ユーザビリティ調査に基づき、作業を正確に、より効率的に完了できます。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>問合せ先</t>
-    </r>
+    <t>型番</t>
+  </si>
+  <si>
+    <t>ICT機器・サービス概要</t>
+  </si>
+  <si>
+    <t>Dynamics 365 Warehouse Management(Android,Windows(UWP),IOS)は、倉庫作業向けモバイルアプリで、直感的で使いやすい新デザインを採用し、倉庫管理ロジックの強化で処理を効率化します。ユーザビリティ調査に基づき、作業を正確に、より効率的に完了できます。</t>
+  </si>
+  <si>
+    <t>問合せ先</t>
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ウェブサイト</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウェブサイトURL</t>
   </si>
   <si>
     <t>https://learn.microsoft.com/ja-jp/dynamics365/supply-chain/warehousing/warehouse-management-overview</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機能性能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配慮対象アクセス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価結果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価不要</t>
-    </r>
+    <t>機能性能</t>
+  </si>
+  <si>
+    <t>配慮対象アクセス</t>
+  </si>
+  <si>
+    <t>評価結果</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>視力なしでの使用（全盲）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>色知覚なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>聴力なしでの使用（全ろう）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた聴力での使用（難聴）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+  </si>
+  <si>
+    <t>発話能力なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた器用さ又は力での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた手の届く範囲での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>光の点滅による影響の最小化（光感受性発作）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>免責事項</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+  </si>
+  <si>
+    <t>プライバシー</t>
+  </si>
+  <si>
+    <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>サポート対応　概要</t>
+  </si>
+  <si>
+    <t>ドキュメントとサポートサービス</t>
+  </si>
+  <si>
+    <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、FAX等）が提供されているか。</t>
+  </si>
+  <si>
+    <t>用いた技術基準</t>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>免責事項</t>
   </si>
   <si>
     <t>章・項・節</t>
@@ -864,18 +262,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -885,84 +283,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -972,11 +334,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -986,22 +348,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -1011,22 +373,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -1036,11 +398,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -1050,138 +412,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -1194,88 +556,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -1285,32 +647,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -1320,88 +682,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -1411,28 +773,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -1442,164 +804,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -1609,7 +971,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1631,13 +993,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1650,26 +1005,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1679,13 +1021,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1699,35 +1056,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="36"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="10.5"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2064,184 +1404,184 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2265,16 +1605,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2340,6 +1680,7 @@
   <rv s="0">
     <v>0</v>
     <v>5</v>
+    <v>Microsoft Dynamics365のロゴ画像</v>
   </rv>
 </rvData>
 </file>
@@ -2349,6 +1690,7 @@
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
   </s>
 </rvStructures>
 </file>
@@ -2675,230 +2017,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EB6FF7-0DB4-4FE2-8363-9025B0F17256}">
-  <sheetPr codeName="Sheet235">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{072CCA13-EB75-4205-ACF4-7E0ACFB9F508}">
+  <sheetPr codeName="Sheet260">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="3"/>
-    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="3"/>
+    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="2"/>
+    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="11" t="e" vm="1">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="2"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -3242,28 +2584,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3313,15 +2655,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3340,11 +2682,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3489,9 +2831,9 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{564F184E-B751-4995-894F-BED036118835}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{5CC89C56-6DCF-4D24-A630-95EA91AFD279}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3499,7 +2841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE49694-1814-41DE-B121-884D6BE90C2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7165A1A3-4E53-4FD1-AEF1-A37D2829A11B}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3524,31 +2866,31 @@
         <v>55</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3556,36 +2898,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3593,10 +2935,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3614,14 +2956,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3637,15 +2979,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3660,15 +3002,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3683,17 +3025,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3706,10 +3048,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3717,7 +3059,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3729,10 +3071,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3741,7 +3083,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3752,10 +3094,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3765,10 +3107,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3777,10 +3119,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3790,10 +3132,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3802,10 +3144,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3823,17 +3165,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3848,10 +3190,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3869,10 +3211,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3887,17 +3229,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3910,17 +3252,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3933,20 +3275,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3958,20 +3300,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3983,17 +3325,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -4009,10 +3351,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -4020,7 +3362,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -4029,23 +3371,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -4054,23 +3396,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4082,15 +3424,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4105,15 +3447,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4128,27 +3470,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4157,10 +3499,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4178,29 +3520,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4209,10 +3551,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4230,17 +3572,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4255,10 +3597,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4276,30 +3618,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4307,10 +3649,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4328,31 +3670,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4361,10 +3703,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4382,15 +3724,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4405,14 +3747,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4428,10 +3770,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4441,10 +3783,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4453,27 +3795,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4482,10 +3824,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4495,10 +3837,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4507,14 +3849,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4530,10 +3872,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4543,10 +3885,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4555,10 +3897,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4568,10 +3910,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4580,10 +3922,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4601,10 +3943,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4622,10 +3964,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4643,14 +3985,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4666,10 +4008,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4687,15 +4029,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4710,10 +4052,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4731,20 +4073,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4756,10 +4098,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4777,29 +4119,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4808,10 +4150,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4829,10 +4171,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4840,7 +4182,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4852,10 +4194,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4863,7 +4205,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4875,10 +4217,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4886,7 +4228,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4898,10 +4240,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4919,24 +4261,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4948,17 +4290,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4971,20 +4313,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4996,10 +4338,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -5017,14 +4359,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -5040,10 +4382,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -5061,22 +4403,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5088,10 +4430,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5109,31 +4451,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5142,10 +4484,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5163,29 +4505,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5194,14 +4536,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5209,10 +4551,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5221,43 +4563,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5267,22 +4609,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5292,22 +4634,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5317,32 +4659,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5351,23 +4693,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5376,26 +4718,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5403,23 +4745,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5431,31 +4773,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5464,10 +4806,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5485,15 +4827,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5508,14 +4850,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5523,10 +4865,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5535,22 +4877,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5562,24 +4904,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5591,10 +4933,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5612,24 +4954,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5638,25 +4980,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5665,20 +5007,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5693,24 +5035,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5722,24 +5064,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5913,7 +5255,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{668931E9-7E53-4CCA-92D0-AC3CCEA5728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8793E9AD-8D33-41A7-BF21-87F11C7D3409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{7C940804-A9F8-4AB4-9BC6-A2510CCAAA97}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F383A13A-B5E0-4FAA-A797-F50D7F4341E5}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -37,35 +37,13 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
   <si>
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年8月6日</t>
+    <t>作成日：2025年8月12日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1635,70 +1613,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-    <v>Microsoft Dynamics365のロゴ画像</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>678543</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>262853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2139043</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1014403</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1" descr="Microsoft Dynamics365のロゴ画像">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D78F1C-74CE-43A5-9C38-3D466D905A12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6101443" y="1209003"/>
+          <a:ext cx="3498850" cy="1564350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2017,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{072CCA13-EB75-4205-ACF4-7E0ACFB9F508}">
-  <sheetPr codeName="Sheet260">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D450E0B7-0524-466B-8B59-E0476A46B0A4}">
+  <sheetPr codeName="Sheet254">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2073,7 +2040,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2084,13 +2051,11 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="10" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="15"/>
@@ -2116,7 +2081,7 @@
       <c r="H6" s="17"/>
       <c r="I6" s="18"/>
     </row>
-    <row r="7" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="13"/>
       <c r="B7" s="14"/>
       <c r="C7" s="15"/>
@@ -2127,7 +2092,7 @@
       <c r="H7" s="17"/>
       <c r="I7" s="18"/>
     </row>
-    <row r="8" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -2140,7 +2105,7 @@
       <c r="H8" s="17"/>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="15"/>
@@ -2151,7 +2116,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="18"/>
     </row>
-    <row r="10" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" ht="82.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -2166,7 +2131,7 @@
       <c r="H10" s="17"/>
       <c r="I10" s="18"/>
     </row>
-    <row r="11" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
@@ -2177,7 +2142,7 @@
       <c r="H11" s="17"/>
       <c r="I11" s="18"/>
     </row>
-    <row r="12" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2157,7 @@
       <c r="H12" s="17"/>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="15"/>
@@ -2203,7 +2168,7 @@
       <c r="H13" s="17"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
@@ -2833,15 +2798,16 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{5CC89C56-6DCF-4D24-A630-95EA91AFD279}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{8322AB0E-B552-47E7-9A48-4DD7D83DAE03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7165A1A3-4E53-4FD1-AEF1-A37D2829A11B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916359EC-2E40-4150-B15C-A10A89BE7280}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
+++ b/file/Dynamics_365_Warehouse_Management_Android_Windows_UWP_IOS_VPATJ05770.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8793E9AD-8D33-41A7-BF21-87F11C7D3409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32F40D16-0423-4F01-8E1D-48C354853CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F383A13A-B5E0-4FAA-A797-F50D7F4341E5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{40317507-4F3A-458F-AFC9-1E15F9BCFBEA}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2025年8月12日</t>
+    <t>作成日：2026年8月6日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1618,22 +1618,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>678543</xdr:colOff>
+      <xdr:colOff>660400</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>262853</xdr:rowOff>
+      <xdr:rowOff>108639</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2139043</xdr:colOff>
+      <xdr:colOff>2120900</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1014403</xdr:rowOff>
+      <xdr:rowOff>856560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1" descr="Microsoft Dynamics365のロゴ画像">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D78F1C-74CE-43A5-9C38-3D466D905A12}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCD2475-D8D8-498B-B76B-EE863CE542EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1655,8 +1655,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6101443" y="1209003"/>
-          <a:ext cx="3498850" cy="1564350"/>
+          <a:off x="6083300" y="1054789"/>
+          <a:ext cx="3498850" cy="1560721"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1984,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D450E0B7-0524-466B-8B59-E0476A46B0A4}">
-  <sheetPr codeName="Sheet254">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43106421-D5A6-4F20-AE28-D6036FDDC348}">
+  <sheetPr codeName="Sheet272">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2116,7 +2116,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="18"/>
     </row>
-    <row r="10" spans="1:9" ht="82.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" ht="73" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -2798,7 +2798,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{8322AB0E-B552-47E7-9A48-4DD7D83DAE03}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{A55282EF-F927-4E2A-BA00-4EA6996B9850}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2807,7 +2807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916359EC-2E40-4150-B15C-A10A89BE7280}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1A4D04-DC7A-4C85-A403-B4E774AE61C4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
